--- a/rules/CORE-002078/negative/01/data/CORE-002078-negative-01.xlsx
+++ b/rules/CORE-002078/negative/01/data/CORE-002078-negative-01.xlsx
@@ -673,7 +673,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -707,7 +707,7 @@
         <v>55</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -727,13 +727,13 @@
         <v>55</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -747,13 +747,13 @@
         <v>55</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -767,13 +767,13 @@
         <v>55</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -787,13 +787,13 @@
         <v>55</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -807,93 +807,13 @@
         <v>55</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1012,10 +932,10 @@
       <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" t="s" s="5">
         <v>51</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" t="s" s="6">
         <v>49</v>
       </c>
       <c r="G5" s="5"/>
@@ -1136,10 +1056,10 @@
       <c r="D11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" t="s" s="5">
         <v>45</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" t="s" s="6">
         <v>50</v>
       </c>
       <c r="G11" s="5" t="s">

--- a/rules/CORE-002078/negative/01/data/CORE-002078-negative-01.xlsx
+++ b/rules/CORE-002078/negative/01/data/CORE-002078-negative-01.xlsx
@@ -673,7 +673,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -707,7 +707,7 @@
         <v>55</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -727,13 +727,13 @@
         <v>55</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -747,13 +747,13 @@
         <v>55</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -767,13 +767,13 @@
         <v>55</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -787,13 +787,13 @@
         <v>55</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -807,13 +807,93 @@
         <v>55</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -932,10 +1012,10 @@
       <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s" s="5">
+      <c r="E5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F5" t="s" s="6">
+      <c r="F5" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G5" s="5"/>
@@ -1056,10 +1136,10 @@
       <c r="D11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E11" t="s" s="5">
+      <c r="E11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F11" t="s" s="6">
+      <c r="F11" s="10" t="s">
         <v>50</v>
       </c>
       <c r="G11" s="5" t="s">
